--- a/data.mn/public/datasets/industrial-output-by-subdivision-monthly.xlsx
+++ b/data.mn/public/datasets/industrial-output-by-subdivision-monthly.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E108"/>
+  <dimension ref="A1:E110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2358,16 +2358,16 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>288.4</v>
+        <v>288.5</v>
       </c>
       <c r="C102" t="n">
-        <v>557.3</v>
+        <v>560.9</v>
       </c>
       <c r="D102" t="n">
-        <v>4224.5</v>
+        <v>4422.5</v>
       </c>
       <c r="E102" t="n">
-        <v>25.3</v>
+        <v>25.4</v>
       </c>
     </row>
     <row r="103">
@@ -2377,16 +2377,16 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>272</v>
+        <v>272.1</v>
       </c>
       <c r="C103" t="n">
-        <v>483.2</v>
+        <v>485.9</v>
       </c>
       <c r="D103" t="n">
-        <v>4431.2</v>
+        <v>4547.7</v>
       </c>
       <c r="E103" t="n">
-        <v>24.7</v>
+        <v>24.8</v>
       </c>
     </row>
     <row r="104">
@@ -2399,7 +2399,7 @@
         <v>267.4</v>
       </c>
       <c r="C104" t="n">
-        <v>557.9</v>
+        <v>560.9</v>
       </c>
       <c r="D104" t="n">
         <v>4997.2</v>
@@ -2418,10 +2418,10 @@
         <v>238</v>
       </c>
       <c r="C105" t="n">
-        <v>664.4</v>
+        <v>668.3</v>
       </c>
       <c r="D105" t="n">
-        <v>4641.1</v>
+        <v>4850.7</v>
       </c>
       <c r="E105" t="n">
         <v>26.7</v>
@@ -2437,10 +2437,10 @@
         <v>194.9</v>
       </c>
       <c r="C106" t="n">
-        <v>814.1</v>
+        <v>815</v>
       </c>
       <c r="D106" t="n">
-        <v>5562.2</v>
+        <v>5562.1</v>
       </c>
       <c r="E106" t="n">
         <v>26.7</v>
@@ -2456,10 +2456,10 @@
         <v>191.4</v>
       </c>
       <c r="C107" t="n">
-        <v>1014.9</v>
+        <v>1019.7</v>
       </c>
       <c r="D107" t="n">
-        <v>5760.1</v>
+        <v>5760</v>
       </c>
       <c r="E107" t="n">
         <v>28.1</v>
@@ -2475,13 +2475,51 @@
         <v>202.1</v>
       </c>
       <c r="C108" t="n">
-        <v>809.4</v>
+        <v>815.2</v>
       </c>
       <c r="D108" t="n">
-        <v>5967.6</v>
+        <v>6016.6</v>
       </c>
       <c r="E108" t="n">
         <v>28.4</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>203.9</v>
+      </c>
+      <c r="C109" t="n">
+        <v>927.1</v>
+      </c>
+      <c r="D109" t="n">
+        <v>5695.7</v>
+      </c>
+      <c r="E109" t="n">
+        <v>29.6</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>221.5</v>
+      </c>
+      <c r="C110" t="n">
+        <v>1072.8</v>
+      </c>
+      <c r="D110" t="n">
+        <v>5907.2</v>
+      </c>
+      <c r="E110" t="n">
+        <v>32.2</v>
       </c>
     </row>
   </sheetData>
@@ -2495,12 +2533,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E108"/>
+  <dimension ref="A1:E110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
     <col width="30" customWidth="1" min="5" max="5"/>
   </cols>
@@ -2513,22 +2551,22 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>Цахилгаан хий, уур, агааржуулалт</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>Боловсруулах үйлдвэрлэл</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Уул уурхай, олборлолт</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
         <is>
           <t>Ус хангамж; бохир ус зайлуулах систем, хог, хаягдлын менежмент болон цэвэрлэх үйл ажиллагаа</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Уул уурхай, олборлолт</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Цахилгаан хий, уур, агааржуулалт</t>
         </is>
       </c>
     </row>
@@ -2539,16 +2577,16 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>56.3</v>
+      </c>
+      <c r="C2" t="n">
         <v>208.9</v>
-      </c>
-      <c r="C2" t="n">
-        <v>45.9</v>
       </c>
       <c r="D2" t="n">
         <v>972.2</v>
       </c>
       <c r="E2" t="n">
-        <v>56.3</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="3">
@@ -2558,16 +2596,16 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="C3" t="n">
         <v>219.6</v>
-      </c>
-      <c r="C3" t="n">
-        <v>47.3</v>
       </c>
       <c r="D3" t="n">
         <v>957.1</v>
       </c>
       <c r="E3" t="n">
-        <v>74.5</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="4">
@@ -2577,16 +2615,16 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>84.09999999999999</v>
+      </c>
+      <c r="C4" t="n">
         <v>212.4</v>
-      </c>
-      <c r="C4" t="n">
-        <v>47.2</v>
       </c>
       <c r="D4" t="n">
         <v>783.9</v>
       </c>
       <c r="E4" t="n">
-        <v>84.09999999999999</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="5">
@@ -2596,16 +2634,16 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>93.40000000000001</v>
+      </c>
+      <c r="C5" t="n">
         <v>231.7</v>
-      </c>
-      <c r="C5" t="n">
-        <v>7.5</v>
       </c>
       <c r="D5" t="n">
         <v>771.6</v>
       </c>
       <c r="E5" t="n">
-        <v>93.40000000000001</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="6">
@@ -2615,16 +2653,16 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>100.1</v>
+      </c>
+      <c r="C6" t="n">
         <v>189.9</v>
-      </c>
-      <c r="C6" t="n">
-        <v>46.5</v>
       </c>
       <c r="D6" t="n">
         <v>815.1</v>
       </c>
       <c r="E6" t="n">
-        <v>100.1</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="7">
@@ -2634,16 +2672,16 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>97.59999999999999</v>
+      </c>
+      <c r="C7" t="n">
         <v>163.6</v>
-      </c>
-      <c r="C7" t="n">
-        <v>47.9</v>
       </c>
       <c r="D7" t="n">
         <v>688</v>
       </c>
       <c r="E7" t="n">
-        <v>97.59999999999999</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="8">
@@ -2653,16 +2691,16 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>91.09999999999999</v>
+      </c>
+      <c r="C8" t="n">
         <v>175.6</v>
-      </c>
-      <c r="C8" t="n">
-        <v>48</v>
       </c>
       <c r="D8" t="n">
         <v>902.5</v>
       </c>
       <c r="E8" t="n">
-        <v>91.09999999999999</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9">
@@ -2672,16 +2710,16 @@
         </is>
       </c>
       <c r="B9" t="n">
+        <v>86.8</v>
+      </c>
+      <c r="C9" t="n">
         <v>221.5</v>
-      </c>
-      <c r="C9" t="n">
-        <v>51</v>
       </c>
       <c r="D9" t="n">
         <v>911.2</v>
       </c>
       <c r="E9" t="n">
-        <v>86.8</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10">
@@ -2691,16 +2729,16 @@
         </is>
       </c>
       <c r="B10" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="C10" t="n">
         <v>280.4</v>
-      </c>
-      <c r="C10" t="n">
-        <v>54</v>
       </c>
       <c r="D10" t="n">
         <v>1101</v>
       </c>
       <c r="E10" t="n">
-        <v>72.2</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11">
@@ -2710,16 +2748,16 @@
         </is>
       </c>
       <c r="B11" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="C11" t="n">
         <v>304.1</v>
-      </c>
-      <c r="C11" t="n">
-        <v>64.3</v>
       </c>
       <c r="D11" t="n">
         <v>1069.4</v>
       </c>
       <c r="E11" t="n">
-        <v>61.2</v>
+        <v>64.3</v>
       </c>
     </row>
     <row r="12">
@@ -2729,16 +2767,16 @@
         </is>
       </c>
       <c r="B12" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="C12" t="n">
         <v>254.9</v>
-      </c>
-      <c r="C12" t="n">
-        <v>42.7</v>
       </c>
       <c r="D12" t="n">
         <v>892.6</v>
       </c>
       <c r="E12" t="n">
-        <v>58.3</v>
+        <v>42.7</v>
       </c>
     </row>
     <row r="13">
@@ -2748,16 +2786,16 @@
         </is>
       </c>
       <c r="B13" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="C13" t="n">
         <v>256</v>
-      </c>
-      <c r="C13" t="n">
-        <v>48.3</v>
       </c>
       <c r="D13" t="n">
         <v>933.7</v>
       </c>
       <c r="E13" t="n">
-        <v>60.2</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="14">
@@ -2767,16 +2805,16 @@
         </is>
       </c>
       <c r="B14" t="n">
+        <v>65</v>
+      </c>
+      <c r="C14" t="n">
         <v>251.1</v>
-      </c>
-      <c r="C14" t="n">
-        <v>49.3</v>
       </c>
       <c r="D14" t="n">
         <v>1067.6</v>
       </c>
       <c r="E14" t="n">
-        <v>65</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="15">
@@ -2786,16 +2824,16 @@
         </is>
       </c>
       <c r="B15" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="C15" t="n">
         <v>302.7</v>
-      </c>
-      <c r="C15" t="n">
-        <v>55.4</v>
       </c>
       <c r="D15" t="n">
         <v>1166.6</v>
       </c>
       <c r="E15" t="n">
-        <v>81.5</v>
+        <v>55.4</v>
       </c>
     </row>
     <row r="16">
@@ -2805,16 +2843,16 @@
         </is>
       </c>
       <c r="B16" t="n">
+        <v>93.3</v>
+      </c>
+      <c r="C16" t="n">
         <v>257.7</v>
-      </c>
-      <c r="C16" t="n">
-        <v>48.7</v>
       </c>
       <c r="D16" t="n">
         <v>1018.1</v>
       </c>
       <c r="E16" t="n">
-        <v>93.3</v>
+        <v>48.7</v>
       </c>
     </row>
     <row r="17">
@@ -2824,16 +2862,16 @@
         </is>
       </c>
       <c r="B17" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="C17" t="n">
         <v>280</v>
-      </c>
-      <c r="C17" t="n">
-        <v>8.800000000000001</v>
       </c>
       <c r="D17" t="n">
         <v>1024.6</v>
       </c>
       <c r="E17" t="n">
-        <v>103.8</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -2843,16 +2881,16 @@
         </is>
       </c>
       <c r="B18" t="n">
+        <v>109.8</v>
+      </c>
+      <c r="C18" t="n">
         <v>237.9</v>
-      </c>
-      <c r="C18" t="n">
-        <v>59.6</v>
       </c>
       <c r="D18" t="n">
         <v>976.1</v>
       </c>
       <c r="E18" t="n">
-        <v>109.8</v>
+        <v>59.6</v>
       </c>
     </row>
     <row r="19">
@@ -2862,16 +2900,16 @@
         </is>
       </c>
       <c r="B19" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="C19" t="n">
         <v>167.1</v>
-      </c>
-      <c r="C19" t="n">
-        <v>59.8</v>
       </c>
       <c r="D19" t="n">
         <v>950.8</v>
       </c>
       <c r="E19" t="n">
-        <v>106.5</v>
+        <v>59.8</v>
       </c>
     </row>
     <row r="20">
@@ -2881,16 +2919,16 @@
         </is>
       </c>
       <c r="B20" t="n">
+        <v>99.3</v>
+      </c>
+      <c r="C20" t="n">
         <v>223.6</v>
-      </c>
-      <c r="C20" t="n">
-        <v>58.1</v>
       </c>
       <c r="D20" t="n">
         <v>1070.7</v>
       </c>
       <c r="E20" t="n">
-        <v>99.3</v>
+        <v>58.1</v>
       </c>
     </row>
     <row r="21">
@@ -2900,16 +2938,16 @@
         </is>
       </c>
       <c r="B21" t="n">
+        <v>96.2</v>
+      </c>
+      <c r="C21" t="n">
         <v>288.9</v>
-      </c>
-      <c r="C21" t="n">
-        <v>57.3</v>
       </c>
       <c r="D21" t="n">
         <v>1070.9</v>
       </c>
       <c r="E21" t="n">
-        <v>96.2</v>
+        <v>57.3</v>
       </c>
     </row>
     <row r="22">
@@ -2919,16 +2957,16 @@
         </is>
       </c>
       <c r="B22" t="n">
+        <v>83.09999999999999</v>
+      </c>
+      <c r="C22" t="n">
         <v>387.3</v>
-      </c>
-      <c r="C22" t="n">
-        <v>58</v>
       </c>
       <c r="D22" t="n">
         <v>1217.6</v>
       </c>
       <c r="E22" t="n">
-        <v>83.09999999999999</v>
+        <v>58</v>
       </c>
     </row>
     <row r="23">
@@ -2938,16 +2976,16 @@
         </is>
       </c>
       <c r="B23" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="C23" t="n">
         <v>318.1</v>
-      </c>
-      <c r="C23" t="n">
-        <v>58.2</v>
       </c>
       <c r="D23" t="n">
         <v>1066.2</v>
       </c>
       <c r="E23" t="n">
-        <v>72.5</v>
+        <v>58.2</v>
       </c>
     </row>
     <row r="24">
@@ -2957,16 +2995,16 @@
         </is>
       </c>
       <c r="B24" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="C24" t="n">
         <v>262.8</v>
-      </c>
-      <c r="C24" t="n">
-        <v>57.5</v>
       </c>
       <c r="D24" t="n">
         <v>1152.9</v>
       </c>
       <c r="E24" t="n">
-        <v>70.2</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="25">
@@ -2976,16 +3014,16 @@
         </is>
       </c>
       <c r="B25" t="n">
+        <v>70.59999999999999</v>
+      </c>
+      <c r="C25" t="n">
         <v>267.1</v>
-      </c>
-      <c r="C25" t="n">
-        <v>57.5</v>
       </c>
       <c r="D25" t="n">
         <v>1271.3</v>
       </c>
       <c r="E25" t="n">
-        <v>70.59999999999999</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="26">
@@ -2995,16 +3033,16 @@
         </is>
       </c>
       <c r="B26" t="n">
+        <v>77.8</v>
+      </c>
+      <c r="C26" t="n">
         <v>281.6</v>
-      </c>
-      <c r="C26" t="n">
-        <v>58.6</v>
       </c>
       <c r="D26" t="n">
         <v>1180.7</v>
       </c>
       <c r="E26" t="n">
-        <v>77.8</v>
+        <v>58.6</v>
       </c>
     </row>
     <row r="27">
@@ -3014,16 +3052,16 @@
         </is>
       </c>
       <c r="B27" t="n">
+        <v>96.40000000000001</v>
+      </c>
+      <c r="C27" t="n">
         <v>288</v>
-      </c>
-      <c r="C27" t="n">
-        <v>58.3</v>
       </c>
       <c r="D27" t="n">
         <v>1227.1</v>
       </c>
       <c r="E27" t="n">
-        <v>96.40000000000001</v>
+        <v>58.3</v>
       </c>
     </row>
     <row r="28">
@@ -3033,16 +3071,16 @@
         </is>
       </c>
       <c r="B28" t="n">
+        <v>114.7</v>
+      </c>
+      <c r="C28" t="n">
         <v>276.3</v>
-      </c>
-      <c r="C28" t="n">
-        <v>59.4</v>
       </c>
       <c r="D28" t="n">
         <v>1112.5</v>
       </c>
       <c r="E28" t="n">
-        <v>114.7</v>
+        <v>59.4</v>
       </c>
     </row>
     <row r="29">
@@ -3052,16 +3090,16 @@
         </is>
       </c>
       <c r="B29" t="n">
+        <v>123.3</v>
+      </c>
+      <c r="C29" t="n">
         <v>281.6</v>
-      </c>
-      <c r="C29" t="n">
-        <v>10.1</v>
       </c>
       <c r="D29" t="n">
         <v>862.5</v>
       </c>
       <c r="E29" t="n">
-        <v>123.3</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="30">
@@ -3071,16 +3109,16 @@
         </is>
       </c>
       <c r="B30" t="n">
+        <v>131</v>
+      </c>
+      <c r="C30" t="n">
         <v>233.7</v>
-      </c>
-      <c r="C30" t="n">
-        <v>10.7</v>
       </c>
       <c r="D30" t="n">
         <v>796.2</v>
       </c>
       <c r="E30" t="n">
-        <v>131</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="31">
@@ -3090,16 +3128,16 @@
         </is>
       </c>
       <c r="B31" t="n">
+        <v>127.2</v>
+      </c>
+      <c r="C31" t="n">
         <v>228</v>
-      </c>
-      <c r="C31" t="n">
-        <v>10.7</v>
       </c>
       <c r="D31" t="n">
         <v>684.9</v>
       </c>
       <c r="E31" t="n">
-        <v>127.2</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="32">
@@ -3109,16 +3147,16 @@
         </is>
       </c>
       <c r="B32" t="n">
+        <v>115.9</v>
+      </c>
+      <c r="C32" t="n">
         <v>206.1</v>
-      </c>
-      <c r="C32" t="n">
-        <v>10.6</v>
       </c>
       <c r="D32" t="n">
         <v>697.8</v>
       </c>
       <c r="E32" t="n">
-        <v>115.9</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="33">
@@ -3128,16 +3166,16 @@
         </is>
       </c>
       <c r="B33" t="n">
+        <v>106</v>
+      </c>
+      <c r="C33" t="n">
         <v>217.6</v>
-      </c>
-      <c r="C33" t="n">
-        <v>11</v>
       </c>
       <c r="D33" t="n">
         <v>621.1</v>
       </c>
       <c r="E33" t="n">
-        <v>106</v>
+        <v>11</v>
       </c>
     </row>
     <row r="34">
@@ -3147,16 +3185,16 @@
         </is>
       </c>
       <c r="B34" t="n">
+        <v>83.7</v>
+      </c>
+      <c r="C34" t="n">
         <v>275.5</v>
-      </c>
-      <c r="C34" t="n">
-        <v>11.2</v>
       </c>
       <c r="D34" t="n">
         <v>837.8</v>
       </c>
       <c r="E34" t="n">
-        <v>83.7</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="35">
@@ -3166,16 +3204,16 @@
         </is>
       </c>
       <c r="B35" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="C35" t="n">
         <v>284.5</v>
-      </c>
-      <c r="C35" t="n">
-        <v>11</v>
       </c>
       <c r="D35" t="n">
         <v>1012</v>
       </c>
       <c r="E35" t="n">
-        <v>72.5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="36">
@@ -3185,16 +3223,16 @@
         </is>
       </c>
       <c r="B36" t="n">
+        <v>68.90000000000001</v>
+      </c>
+      <c r="C36" t="n">
         <v>281.2</v>
-      </c>
-      <c r="C36" t="n">
-        <v>11</v>
       </c>
       <c r="D36" t="n">
         <v>1043.8</v>
       </c>
       <c r="E36" t="n">
-        <v>68.90000000000001</v>
+        <v>11</v>
       </c>
     </row>
     <row r="37">
@@ -3204,16 +3242,16 @@
         </is>
       </c>
       <c r="B37" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="C37" t="n">
         <v>319</v>
-      </c>
-      <c r="C37" t="n">
-        <v>11</v>
       </c>
       <c r="D37" t="n">
         <v>1020.2</v>
       </c>
       <c r="E37" t="n">
-        <v>70.2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="38">
@@ -3223,16 +3261,16 @@
         </is>
       </c>
       <c r="B38" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="C38" t="n">
         <v>299.1</v>
-      </c>
-      <c r="C38" t="n">
-        <v>11</v>
       </c>
       <c r="D38" t="n">
         <v>1285.5</v>
       </c>
       <c r="E38" t="n">
-        <v>76.7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="39">
@@ -3242,16 +3280,16 @@
         </is>
       </c>
       <c r="B39" t="n">
+        <v>102</v>
+      </c>
+      <c r="C39" t="n">
         <v>318.6</v>
-      </c>
-      <c r="C39" t="n">
-        <v>11.9</v>
       </c>
       <c r="D39" t="n">
         <v>1479.7</v>
       </c>
       <c r="E39" t="n">
-        <v>102</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="40">
@@ -3261,16 +3299,16 @@
         </is>
       </c>
       <c r="B40" t="n">
+        <v>116.6</v>
+      </c>
+      <c r="C40" t="n">
         <v>238.8</v>
-      </c>
-      <c r="C40" t="n">
-        <v>11.1</v>
       </c>
       <c r="D40" t="n">
         <v>1363.5</v>
       </c>
       <c r="E40" t="n">
-        <v>116.6</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="41">
@@ -3280,16 +3318,16 @@
         </is>
       </c>
       <c r="B41" t="n">
+        <v>129.9</v>
+      </c>
+      <c r="C41" t="n">
         <v>268.6</v>
-      </c>
-      <c r="C41" t="n">
-        <v>12.4</v>
       </c>
       <c r="D41" t="n">
         <v>1390.6</v>
       </c>
       <c r="E41" t="n">
-        <v>129.9</v>
+        <v>12.4</v>
       </c>
     </row>
     <row r="42">
@@ -3299,16 +3337,16 @@
         </is>
       </c>
       <c r="B42" t="n">
+        <v>138.3</v>
+      </c>
+      <c r="C42" t="n">
         <v>283.1</v>
-      </c>
-      <c r="C42" t="n">
-        <v>11.6</v>
       </c>
       <c r="D42" t="n">
         <v>945.3</v>
       </c>
       <c r="E42" t="n">
-        <v>138.3</v>
+        <v>11.6</v>
       </c>
     </row>
     <row r="43">
@@ -3318,16 +3356,16 @@
         </is>
       </c>
       <c r="B43" t="n">
+        <v>136.7</v>
+      </c>
+      <c r="C43" t="n">
         <v>257.6</v>
-      </c>
-      <c r="C43" t="n">
-        <v>11.9</v>
       </c>
       <c r="D43" t="n">
         <v>899.2</v>
       </c>
       <c r="E43" t="n">
-        <v>136.7</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="44">
@@ -3337,16 +3375,16 @@
         </is>
       </c>
       <c r="B44" t="n">
+        <v>127</v>
+      </c>
+      <c r="C44" t="n">
         <v>315.9</v>
-      </c>
-      <c r="C44" t="n">
-        <v>13.3</v>
       </c>
       <c r="D44" t="n">
         <v>1106.1</v>
       </c>
       <c r="E44" t="n">
-        <v>127</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="45">
@@ -3356,16 +3394,16 @@
         </is>
       </c>
       <c r="B45" t="n">
+        <v>116.3</v>
+      </c>
+      <c r="C45" t="n">
         <v>304.3</v>
-      </c>
-      <c r="C45" t="n">
-        <v>13.4</v>
       </c>
       <c r="D45" t="n">
         <v>1035.4</v>
       </c>
       <c r="E45" t="n">
-        <v>116.3</v>
+        <v>13.4</v>
       </c>
     </row>
     <row r="46">
@@ -3375,16 +3413,16 @@
         </is>
       </c>
       <c r="B46" t="n">
+        <v>97.8</v>
+      </c>
+      <c r="C46" t="n">
         <v>442.3</v>
-      </c>
-      <c r="C46" t="n">
-        <v>13.1</v>
       </c>
       <c r="D46" t="n">
         <v>1136.3</v>
       </c>
       <c r="E46" t="n">
-        <v>97.8</v>
+        <v>13.1</v>
       </c>
     </row>
     <row r="47">
@@ -3394,16 +3432,16 @@
         </is>
       </c>
       <c r="B47" t="n">
+        <v>84.59999999999999</v>
+      </c>
+      <c r="C47" t="n">
         <v>444.8</v>
-      </c>
-      <c r="C47" t="n">
-        <v>13.9</v>
       </c>
       <c r="D47" t="n">
         <v>1082.1</v>
       </c>
       <c r="E47" t="n">
-        <v>84.59999999999999</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="48">
@@ -3413,16 +3451,16 @@
         </is>
       </c>
       <c r="B48" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="C48" t="n">
         <v>298.6</v>
-      </c>
-      <c r="C48" t="n">
-        <v>12.8</v>
       </c>
       <c r="D48" t="n">
         <v>1045.3</v>
       </c>
       <c r="E48" t="n">
-        <v>73.8</v>
+        <v>12.8</v>
       </c>
     </row>
     <row r="49">
@@ -3432,16 +3470,16 @@
         </is>
       </c>
       <c r="B49" t="n">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="C49" t="n">
         <v>336.1</v>
-      </c>
-      <c r="C49" t="n">
-        <v>12.9</v>
       </c>
       <c r="D49" t="n">
         <v>1060.6</v>
       </c>
       <c r="E49" t="n">
-        <v>79.09999999999999</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="50">
@@ -3451,16 +3489,16 @@
         </is>
       </c>
       <c r="B50" t="n">
+        <v>89.7</v>
+      </c>
+      <c r="C50" t="n">
         <v>320.1</v>
-      </c>
-      <c r="C50" t="n">
-        <v>14</v>
       </c>
       <c r="D50" t="n">
         <v>1033.6</v>
       </c>
       <c r="E50" t="n">
-        <v>89.7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="51">
@@ -3470,16 +3508,16 @@
         </is>
       </c>
       <c r="B51" t="n">
+        <v>117.4</v>
+      </c>
+      <c r="C51" t="n">
         <v>342</v>
-      </c>
-      <c r="C51" t="n">
-        <v>18.2</v>
       </c>
       <c r="D51" t="n">
         <v>1150.5</v>
       </c>
       <c r="E51" t="n">
-        <v>117.4</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="52">
@@ -3489,16 +3527,16 @@
         </is>
       </c>
       <c r="B52" t="n">
+        <v>134.5</v>
+      </c>
+      <c r="C52" t="n">
         <v>379.7</v>
-      </c>
-      <c r="C52" t="n">
-        <v>17.9</v>
       </c>
       <c r="D52" t="n">
         <v>1005.9</v>
       </c>
       <c r="E52" t="n">
-        <v>134.5</v>
+        <v>17.9</v>
       </c>
     </row>
     <row r="53">
@@ -3508,16 +3546,16 @@
         </is>
       </c>
       <c r="B53" t="n">
+        <v>156.5</v>
+      </c>
+      <c r="C53" t="n">
         <v>464.4</v>
-      </c>
-      <c r="C53" t="n">
-        <v>19.4</v>
       </c>
       <c r="D53" t="n">
         <v>901</v>
       </c>
       <c r="E53" t="n">
-        <v>156.5</v>
+        <v>19.4</v>
       </c>
     </row>
     <row r="54">
@@ -3527,16 +3565,16 @@
         </is>
       </c>
       <c r="B54" t="n">
+        <v>148.5</v>
+      </c>
+      <c r="C54" t="n">
         <v>371.1</v>
-      </c>
-      <c r="C54" t="n">
-        <v>12.7</v>
       </c>
       <c r="D54" t="n">
         <v>1120.7</v>
       </c>
       <c r="E54" t="n">
-        <v>148.5</v>
+        <v>12.7</v>
       </c>
     </row>
     <row r="55">
@@ -3546,16 +3584,16 @@
         </is>
       </c>
       <c r="B55" t="n">
+        <v>145.3</v>
+      </c>
+      <c r="C55" t="n">
         <v>241.7</v>
-      </c>
-      <c r="C55" t="n">
-        <v>15.1</v>
       </c>
       <c r="D55" t="n">
         <v>900.3</v>
       </c>
       <c r="E55" t="n">
-        <v>145.3</v>
+        <v>15.1</v>
       </c>
     </row>
     <row r="56">
@@ -3565,16 +3603,16 @@
         </is>
       </c>
       <c r="B56" t="n">
+        <v>135</v>
+      </c>
+      <c r="C56" t="n">
         <v>296.7</v>
-      </c>
-      <c r="C56" t="n">
-        <v>15.6</v>
       </c>
       <c r="D56" t="n">
         <v>981</v>
       </c>
       <c r="E56" t="n">
-        <v>135</v>
+        <v>15.6</v>
       </c>
     </row>
     <row r="57">
@@ -3584,16 +3622,16 @@
         </is>
       </c>
       <c r="B57" t="n">
+        <v>124</v>
+      </c>
+      <c r="C57" t="n">
         <v>365.6</v>
-      </c>
-      <c r="C57" t="n">
-        <v>17.1</v>
       </c>
       <c r="D57" t="n">
         <v>1209.3</v>
       </c>
       <c r="E57" t="n">
-        <v>124</v>
+        <v>17.1</v>
       </c>
     </row>
     <row r="58">
@@ -3603,16 +3641,16 @@
         </is>
       </c>
       <c r="B58" t="n">
+        <v>100.9</v>
+      </c>
+      <c r="C58" t="n">
         <v>526.4</v>
-      </c>
-      <c r="C58" t="n">
-        <v>16.1</v>
       </c>
       <c r="D58" t="n">
         <v>1224.1</v>
       </c>
       <c r="E58" t="n">
-        <v>100.9</v>
+        <v>16.1</v>
       </c>
     </row>
     <row r="59">
@@ -3622,16 +3660,16 @@
         </is>
       </c>
       <c r="B59" t="n">
+        <v>84.09999999999999</v>
+      </c>
+      <c r="C59" t="n">
         <v>566.4</v>
-      </c>
-      <c r="C59" t="n">
-        <v>16.1</v>
       </c>
       <c r="D59" t="n">
         <v>1388.4</v>
       </c>
       <c r="E59" t="n">
-        <v>84.09999999999999</v>
+        <v>16.1</v>
       </c>
     </row>
     <row r="60">
@@ -3641,16 +3679,16 @@
         </is>
       </c>
       <c r="B60" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="C60" t="n">
         <v>414.7</v>
-      </c>
-      <c r="C60" t="n">
-        <v>15.3</v>
       </c>
       <c r="D60" t="n">
         <v>1397.7</v>
       </c>
       <c r="E60" t="n">
-        <v>78.5</v>
+        <v>15.3</v>
       </c>
     </row>
     <row r="61">
@@ -3660,16 +3698,16 @@
         </is>
       </c>
       <c r="B61" t="n">
+        <v>82.40000000000001</v>
+      </c>
+      <c r="C61" t="n">
         <v>486.4</v>
-      </c>
-      <c r="C61" t="n">
-        <v>15.9</v>
       </c>
       <c r="D61" t="n">
         <v>1979.1</v>
       </c>
       <c r="E61" t="n">
-        <v>82.40000000000001</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="62">
@@ -3679,16 +3717,16 @@
         </is>
       </c>
       <c r="B62" t="n">
+        <v>93.7</v>
+      </c>
+      <c r="C62" t="n">
         <v>453.1</v>
-      </c>
-      <c r="C62" t="n">
-        <v>17.6</v>
       </c>
       <c r="D62" t="n">
         <v>2026.4</v>
       </c>
       <c r="E62" t="n">
-        <v>93.7</v>
+        <v>17.6</v>
       </c>
     </row>
     <row r="63">
@@ -3698,16 +3736,16 @@
         </is>
       </c>
       <c r="B63" t="n">
+        <v>128</v>
+      </c>
+      <c r="C63" t="n">
         <v>502.5</v>
-      </c>
-      <c r="C63" t="n">
-        <v>17.1</v>
       </c>
       <c r="D63" t="n">
         <v>2175.3</v>
       </c>
       <c r="E63" t="n">
-        <v>128</v>
+        <v>17.1</v>
       </c>
     </row>
     <row r="64">
@@ -3717,16 +3755,16 @@
         </is>
       </c>
       <c r="B64" t="n">
+        <v>149.3</v>
+      </c>
+      <c r="C64" t="n">
         <v>410.5</v>
-      </c>
-      <c r="C64" t="n">
-        <v>16.9</v>
       </c>
       <c r="D64" t="n">
         <v>2059.7</v>
       </c>
       <c r="E64" t="n">
-        <v>149.3</v>
+        <v>16.9</v>
       </c>
     </row>
     <row r="65">
@@ -3736,16 +3774,16 @@
         </is>
       </c>
       <c r="B65" t="n">
+        <v>185.3</v>
+      </c>
+      <c r="C65" t="n">
         <v>516.8</v>
-      </c>
-      <c r="C65" t="n">
-        <v>18.8</v>
       </c>
       <c r="D65" t="n">
         <v>2075.7</v>
       </c>
       <c r="E65" t="n">
-        <v>185.3</v>
+        <v>18.8</v>
       </c>
     </row>
     <row r="66">
@@ -3755,16 +3793,16 @@
         </is>
       </c>
       <c r="B66" t="n">
+        <v>197.8</v>
+      </c>
+      <c r="C66" t="n">
         <v>431</v>
-      </c>
-      <c r="C66" t="n">
-        <v>18.4</v>
       </c>
       <c r="D66" t="n">
         <v>2304.7</v>
       </c>
       <c r="E66" t="n">
-        <v>197.8</v>
+        <v>18.4</v>
       </c>
     </row>
     <row r="67">
@@ -3774,16 +3812,16 @@
         </is>
       </c>
       <c r="B67" t="n">
+        <v>177.4</v>
+      </c>
+      <c r="C67" t="n">
         <v>403.6</v>
-      </c>
-      <c r="C67" t="n">
-        <v>18.2</v>
       </c>
       <c r="D67" t="n">
         <v>2073.2</v>
       </c>
       <c r="E67" t="n">
-        <v>177.4</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="68">
@@ -3793,16 +3831,16 @@
         </is>
       </c>
       <c r="B68" t="n">
+        <v>155.7</v>
+      </c>
+      <c r="C68" t="n">
         <v>457</v>
-      </c>
-      <c r="C68" t="n">
-        <v>18.6</v>
       </c>
       <c r="D68" t="n">
         <v>2471.9</v>
       </c>
       <c r="E68" t="n">
-        <v>155.7</v>
+        <v>18.6</v>
       </c>
     </row>
     <row r="69">
@@ -3812,16 +3850,16 @@
         </is>
       </c>
       <c r="B69" t="n">
+        <v>177.6</v>
+      </c>
+      <c r="C69" t="n">
         <v>437.3</v>
-      </c>
-      <c r="C69" t="n">
-        <v>18.9</v>
       </c>
       <c r="D69" t="n">
         <v>2457.3</v>
       </c>
       <c r="E69" t="n">
-        <v>177.6</v>
+        <v>18.9</v>
       </c>
     </row>
     <row r="70">
@@ -3831,16 +3869,16 @@
         </is>
       </c>
       <c r="B70" t="n">
+        <v>135.6</v>
+      </c>
+      <c r="C70" t="n">
         <v>611.1</v>
-      </c>
-      <c r="C70" t="n">
-        <v>17.5</v>
       </c>
       <c r="D70" t="n">
         <v>2329.5</v>
       </c>
       <c r="E70" t="n">
-        <v>135.6</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="71">
@@ -3850,16 +3888,16 @@
         </is>
       </c>
       <c r="B71" t="n">
+        <v>112.1</v>
+      </c>
+      <c r="C71" t="n">
         <v>697.1</v>
-      </c>
-      <c r="C71" t="n">
-        <v>17.9</v>
       </c>
       <c r="D71" t="n">
         <v>2325.7</v>
       </c>
       <c r="E71" t="n">
-        <v>112.1</v>
+        <v>17.9</v>
       </c>
     </row>
     <row r="72">
@@ -3869,16 +3907,16 @@
         </is>
       </c>
       <c r="B72" t="n">
+        <v>108.2</v>
+      </c>
+      <c r="C72" t="n">
         <v>630.2</v>
-      </c>
-      <c r="C72" t="n">
-        <v>16.3</v>
       </c>
       <c r="D72" t="n">
         <v>2251.5</v>
       </c>
       <c r="E72" t="n">
-        <v>108.2</v>
+        <v>16.3</v>
       </c>
     </row>
     <row r="73">
@@ -3888,16 +3926,16 @@
         </is>
       </c>
       <c r="B73" t="n">
+        <v>112.2</v>
+      </c>
+      <c r="C73" t="n">
         <v>724</v>
-      </c>
-      <c r="C73" t="n">
-        <v>17.2</v>
       </c>
       <c r="D73" t="n">
         <v>2952.7</v>
       </c>
       <c r="E73" t="n">
-        <v>112.2</v>
+        <v>17.2</v>
       </c>
     </row>
     <row r="74">
@@ -3907,16 +3945,16 @@
         </is>
       </c>
       <c r="B74" t="n">
+        <v>125.2</v>
+      </c>
+      <c r="C74" t="n">
         <v>628.7</v>
-      </c>
-      <c r="C74" t="n">
-        <v>20.2</v>
       </c>
       <c r="D74" t="n">
         <v>2979.3</v>
       </c>
       <c r="E74" t="n">
-        <v>125.2</v>
+        <v>20.2</v>
       </c>
     </row>
     <row r="75">
@@ -3926,16 +3964,16 @@
         </is>
       </c>
       <c r="B75" t="n">
+        <v>152.3</v>
+      </c>
+      <c r="C75" t="n">
         <v>656.7</v>
-      </c>
-      <c r="C75" t="n">
-        <v>19.9</v>
       </c>
       <c r="D75" t="n">
         <v>2857.9</v>
       </c>
       <c r="E75" t="n">
-        <v>152.3</v>
+        <v>19.9</v>
       </c>
     </row>
     <row r="76">
@@ -3945,16 +3983,16 @@
         </is>
       </c>
       <c r="B76" t="n">
+        <v>191.7</v>
+      </c>
+      <c r="C76" t="n">
         <v>615.6</v>
-      </c>
-      <c r="C76" t="n">
-        <v>21.2</v>
       </c>
       <c r="D76" t="n">
         <v>2990.2</v>
       </c>
       <c r="E76" t="n">
-        <v>191.7</v>
+        <v>21.2</v>
       </c>
     </row>
     <row r="77">
@@ -3964,16 +4002,16 @@
         </is>
       </c>
       <c r="B77" t="n">
+        <v>203</v>
+      </c>
+      <c r="C77" t="n">
         <v>712.8</v>
-      </c>
-      <c r="C77" t="n">
-        <v>23.2</v>
       </c>
       <c r="D77" t="n">
         <v>2912.3</v>
       </c>
       <c r="E77" t="n">
-        <v>203</v>
+        <v>23.2</v>
       </c>
     </row>
     <row r="78">
@@ -3983,16 +4021,16 @@
         </is>
       </c>
       <c r="B78" t="n">
+        <v>211.8</v>
+      </c>
+      <c r="C78" t="n">
         <v>544.6</v>
-      </c>
-      <c r="C78" t="n">
-        <v>22.4</v>
       </c>
       <c r="D78" t="n">
         <v>2878.5</v>
       </c>
       <c r="E78" t="n">
-        <v>211.8</v>
+        <v>22.4</v>
       </c>
     </row>
     <row r="79">
@@ -4002,16 +4040,16 @@
         </is>
       </c>
       <c r="B79" t="n">
+        <v>206.6</v>
+      </c>
+      <c r="C79" t="n">
         <v>391.3</v>
-      </c>
-      <c r="C79" t="n">
-        <v>21.9</v>
       </c>
       <c r="D79" t="n">
         <v>3056.5</v>
       </c>
       <c r="E79" t="n">
-        <v>206.6</v>
+        <v>21.9</v>
       </c>
     </row>
     <row r="80">
@@ -4021,16 +4059,16 @@
         </is>
       </c>
       <c r="B80" t="n">
+        <v>191</v>
+      </c>
+      <c r="C80" t="n">
         <v>477.6</v>
-      </c>
-      <c r="C80" t="n">
-        <v>21.6</v>
       </c>
       <c r="D80" t="n">
         <v>3622.6</v>
       </c>
       <c r="E80" t="n">
-        <v>191</v>
+        <v>21.6</v>
       </c>
     </row>
     <row r="81">
@@ -4040,16 +4078,16 @@
         </is>
       </c>
       <c r="B81" t="n">
+        <v>166.1</v>
+      </c>
+      <c r="C81" t="n">
         <v>513.5</v>
-      </c>
-      <c r="C81" t="n">
-        <v>22.4</v>
       </c>
       <c r="D81" t="n">
         <v>3693.5</v>
       </c>
       <c r="E81" t="n">
-        <v>166.1</v>
+        <v>22.4</v>
       </c>
     </row>
     <row r="82">
@@ -4059,16 +4097,16 @@
         </is>
       </c>
       <c r="B82" t="n">
+        <v>139.6</v>
+      </c>
+      <c r="C82" t="n">
         <v>699.8</v>
-      </c>
-      <c r="C82" t="n">
-        <v>23.1</v>
       </c>
       <c r="D82" t="n">
         <v>3944.4</v>
       </c>
       <c r="E82" t="n">
-        <v>139.6</v>
+        <v>23.1</v>
       </c>
     </row>
     <row r="83">
@@ -4078,16 +4116,16 @@
         </is>
       </c>
       <c r="B83" t="n">
+        <v>121.1</v>
+      </c>
+      <c r="C83" t="n">
         <v>741.2</v>
-      </c>
-      <c r="C83" t="n">
-        <v>22.2</v>
       </c>
       <c r="D83" t="n">
         <v>3815.6</v>
       </c>
       <c r="E83" t="n">
-        <v>121.1</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="84">
@@ -4097,16 +4135,16 @@
         </is>
       </c>
       <c r="B84" t="n">
+        <v>112.3</v>
+      </c>
+      <c r="C84" t="n">
         <v>664.1</v>
-      </c>
-      <c r="C84" t="n">
-        <v>21.8</v>
       </c>
       <c r="D84" t="n">
         <v>3303.8</v>
       </c>
       <c r="E84" t="n">
-        <v>112.3</v>
+        <v>21.8</v>
       </c>
     </row>
     <row r="85">
@@ -4116,16 +4154,16 @@
         </is>
       </c>
       <c r="B85" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="C85" t="n">
         <v>674</v>
-      </c>
-      <c r="C85" t="n">
-        <v>21.3</v>
       </c>
       <c r="D85" t="n">
         <v>3268</v>
       </c>
       <c r="E85" t="n">
-        <v>115.2</v>
+        <v>21.3</v>
       </c>
     </row>
     <row r="86">
@@ -4135,16 +4173,16 @@
         </is>
       </c>
       <c r="B86" t="n">
+        <v>134.1</v>
+      </c>
+      <c r="C86" t="n">
         <v>664.5</v>
-      </c>
-      <c r="C86" t="n">
-        <v>22.3</v>
       </c>
       <c r="D86" t="n">
         <v>3353.2</v>
       </c>
       <c r="E86" t="n">
-        <v>134.1</v>
+        <v>22.3</v>
       </c>
     </row>
     <row r="87">
@@ -4154,16 +4192,16 @@
         </is>
       </c>
       <c r="B87" t="n">
+        <v>176.1</v>
+      </c>
+      <c r="C87" t="n">
         <v>650</v>
-      </c>
-      <c r="C87" t="n">
-        <v>25</v>
       </c>
       <c r="D87" t="n">
         <v>3702.1</v>
       </c>
       <c r="E87" t="n">
-        <v>176.1</v>
+        <v>25</v>
       </c>
     </row>
     <row r="88">
@@ -4173,16 +4211,16 @@
         </is>
       </c>
       <c r="B88" t="n">
+        <v>202</v>
+      </c>
+      <c r="C88" t="n">
         <v>618.6</v>
-      </c>
-      <c r="C88" t="n">
-        <v>25.1</v>
       </c>
       <c r="D88" t="n">
         <v>3239</v>
       </c>
       <c r="E88" t="n">
-        <v>202</v>
+        <v>25.1</v>
       </c>
     </row>
     <row r="89">
@@ -4192,16 +4230,16 @@
         </is>
       </c>
       <c r="B89" t="n">
+        <v>259</v>
+      </c>
+      <c r="C89" t="n">
         <v>627.3</v>
-      </c>
-      <c r="C89" t="n">
-        <v>24.4</v>
       </c>
       <c r="D89" t="n">
         <v>3191.4</v>
       </c>
       <c r="E89" t="n">
-        <v>259</v>
+        <v>24.4</v>
       </c>
     </row>
     <row r="90">
@@ -4211,16 +4249,16 @@
         </is>
       </c>
       <c r="B90" t="n">
+        <v>272.8</v>
+      </c>
+      <c r="C90" t="n">
         <v>543.3</v>
-      </c>
-      <c r="C90" t="n">
-        <v>26.2</v>
       </c>
       <c r="D90" t="n">
         <v>2651.9</v>
       </c>
       <c r="E90" t="n">
-        <v>272.8</v>
+        <v>26.2</v>
       </c>
     </row>
     <row r="91">
@@ -4230,16 +4268,16 @@
         </is>
       </c>
       <c r="B91" t="n">
+        <v>260.5</v>
+      </c>
+      <c r="C91" t="n">
         <v>553</v>
-      </c>
-      <c r="C91" t="n">
-        <v>25</v>
       </c>
       <c r="D91" t="n">
         <v>2461.3</v>
       </c>
       <c r="E91" t="n">
-        <v>260.5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="92">
@@ -4249,16 +4287,16 @@
         </is>
       </c>
       <c r="B92" t="n">
+        <v>241.5</v>
+      </c>
+      <c r="C92" t="n">
         <v>457</v>
-      </c>
-      <c r="C92" t="n">
-        <v>25.3</v>
       </c>
       <c r="D92" t="n">
         <v>2744.8</v>
       </c>
       <c r="E92" t="n">
-        <v>241.5</v>
+        <v>25.3</v>
       </c>
     </row>
     <row r="93">
@@ -4268,16 +4306,16 @@
         </is>
       </c>
       <c r="B93" t="n">
+        <v>222.6</v>
+      </c>
+      <c r="C93" t="n">
         <v>532.9</v>
-      </c>
-      <c r="C93" t="n">
-        <v>25.6</v>
       </c>
       <c r="D93" t="n">
         <v>3249.5</v>
       </c>
       <c r="E93" t="n">
-        <v>222.6</v>
+        <v>25.6</v>
       </c>
     </row>
     <row r="94">
@@ -4287,16 +4325,16 @@
         </is>
       </c>
       <c r="B94" t="n">
+        <v>201.5</v>
+      </c>
+      <c r="C94" t="n">
         <v>674</v>
-      </c>
-      <c r="C94" t="n">
-        <v>26.3</v>
       </c>
       <c r="D94" t="n">
         <v>3575</v>
       </c>
       <c r="E94" t="n">
-        <v>201.5</v>
+        <v>26.3</v>
       </c>
     </row>
     <row r="95">
@@ -4306,16 +4344,16 @@
         </is>
       </c>
       <c r="B95" t="n">
+        <v>165.5</v>
+      </c>
+      <c r="C95" t="n">
         <v>755.4</v>
-      </c>
-      <c r="C95" t="n">
-        <v>24.2</v>
       </c>
       <c r="D95" t="n">
         <v>2924</v>
       </c>
       <c r="E95" t="n">
-        <v>165.5</v>
+        <v>24.2</v>
       </c>
     </row>
     <row r="96">
@@ -4325,16 +4363,16 @@
         </is>
       </c>
       <c r="B96" t="n">
+        <v>157.7</v>
+      </c>
+      <c r="C96" t="n">
         <v>638.8</v>
-      </c>
-      <c r="C96" t="n">
-        <v>22.4</v>
       </c>
       <c r="D96" t="n">
         <v>3559.1</v>
       </c>
       <c r="E96" t="n">
-        <v>157.7</v>
+        <v>22.4</v>
       </c>
     </row>
     <row r="97">
@@ -4344,16 +4382,16 @@
         </is>
       </c>
       <c r="B97" t="n">
+        <v>164.7</v>
+      </c>
+      <c r="C97" t="n">
         <v>896.6</v>
-      </c>
-      <c r="C97" t="n">
-        <v>22.6</v>
       </c>
       <c r="D97" t="n">
         <v>3791.7</v>
       </c>
       <c r="E97" t="n">
-        <v>164.7</v>
+        <v>22.6</v>
       </c>
     </row>
     <row r="98">
@@ -4363,16 +4401,16 @@
         </is>
       </c>
       <c r="B98" t="n">
+        <v>179.5</v>
+      </c>
+      <c r="C98" t="n">
         <v>927.1</v>
-      </c>
-      <c r="C98" t="n">
-        <v>27.1</v>
       </c>
       <c r="D98" t="n">
         <v>3850.4</v>
       </c>
       <c r="E98" t="n">
-        <v>179.5</v>
+        <v>27.1</v>
       </c>
     </row>
     <row r="99">
@@ -4382,16 +4420,16 @@
         </is>
       </c>
       <c r="B99" t="n">
+        <v>236.8</v>
+      </c>
+      <c r="C99" t="n">
         <v>849</v>
-      </c>
-      <c r="C99" t="n">
-        <v>27.7</v>
       </c>
       <c r="D99" t="n">
         <v>4206.2</v>
       </c>
       <c r="E99" t="n">
-        <v>236.8</v>
+        <v>27.7</v>
       </c>
     </row>
     <row r="100">
@@ -4401,16 +4439,16 @@
         </is>
       </c>
       <c r="B100" t="n">
+        <v>269.9</v>
+      </c>
+      <c r="C100" t="n">
         <v>703.8</v>
-      </c>
-      <c r="C100" t="n">
-        <v>26</v>
       </c>
       <c r="D100" t="n">
         <v>4284.3</v>
       </c>
       <c r="E100" t="n">
-        <v>269.9</v>
+        <v>26</v>
       </c>
     </row>
     <row r="101">
@@ -4420,16 +4458,16 @@
         </is>
       </c>
       <c r="B101" t="n">
+        <v>299.9</v>
+      </c>
+      <c r="C101" t="n">
         <v>760.8</v>
-      </c>
-      <c r="C101" t="n">
-        <v>25.9</v>
       </c>
       <c r="D101" t="n">
         <v>4774.1</v>
       </c>
       <c r="E101" t="n">
-        <v>299.9</v>
+        <v>25.9</v>
       </c>
     </row>
     <row r="102">
@@ -4439,16 +4477,16 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>557.3</v>
+        <v>288.5</v>
       </c>
       <c r="C102" t="n">
-        <v>25.3</v>
+        <v>560.9</v>
       </c>
       <c r="D102" t="n">
-        <v>4224.5</v>
+        <v>4422.5</v>
       </c>
       <c r="E102" t="n">
-        <v>288.4</v>
+        <v>25.4</v>
       </c>
     </row>
     <row r="103">
@@ -4458,16 +4496,16 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>483.2</v>
+        <v>272.1</v>
       </c>
       <c r="C103" t="n">
-        <v>24.7</v>
+        <v>485.9</v>
       </c>
       <c r="D103" t="n">
-        <v>4431.2</v>
+        <v>4547.7</v>
       </c>
       <c r="E103" t="n">
-        <v>272</v>
+        <v>24.8</v>
       </c>
     </row>
     <row r="104">
@@ -4477,16 +4515,16 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>557.9</v>
+        <v>267.4</v>
       </c>
       <c r="C104" t="n">
-        <v>25.8</v>
+        <v>560.9</v>
       </c>
       <c r="D104" t="n">
         <v>4997.2</v>
       </c>
       <c r="E104" t="n">
-        <v>267.4</v>
+        <v>25.8</v>
       </c>
     </row>
     <row r="105">
@@ -4496,16 +4534,16 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>664.4</v>
+        <v>238</v>
       </c>
       <c r="C105" t="n">
+        <v>668.3</v>
+      </c>
+      <c r="D105" t="n">
+        <v>4850.7</v>
+      </c>
+      <c r="E105" t="n">
         <v>26.7</v>
-      </c>
-      <c r="D105" t="n">
-        <v>4641.1</v>
-      </c>
-      <c r="E105" t="n">
-        <v>238</v>
       </c>
     </row>
     <row r="106">
@@ -4515,16 +4553,16 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>814.1</v>
+        <v>194.9</v>
       </c>
       <c r="C106" t="n">
+        <v>815</v>
+      </c>
+      <c r="D106" t="n">
+        <v>5562.1</v>
+      </c>
+      <c r="E106" t="n">
         <v>26.7</v>
-      </c>
-      <c r="D106" t="n">
-        <v>5562.2</v>
-      </c>
-      <c r="E106" t="n">
-        <v>194.9</v>
       </c>
     </row>
     <row r="107">
@@ -4534,16 +4572,16 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>1014.9</v>
+        <v>191.4</v>
       </c>
       <c r="C107" t="n">
+        <v>1019.7</v>
+      </c>
+      <c r="D107" t="n">
+        <v>5760</v>
+      </c>
+      <c r="E107" t="n">
         <v>28.1</v>
-      </c>
-      <c r="D107" t="n">
-        <v>5760.1</v>
-      </c>
-      <c r="E107" t="n">
-        <v>191.4</v>
       </c>
     </row>
     <row r="108">
@@ -4553,16 +4591,54 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>809.4</v>
+        <v>202.1</v>
       </c>
       <c r="C108" t="n">
+        <v>815.2</v>
+      </c>
+      <c r="D108" t="n">
+        <v>6016.6</v>
+      </c>
+      <c r="E108" t="n">
         <v>28.4</v>
       </c>
-      <c r="D108" t="n">
-        <v>5967.6</v>
-      </c>
-      <c r="E108" t="n">
-        <v>202.1</v>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>203.9</v>
+      </c>
+      <c r="C109" t="n">
+        <v>927.1</v>
+      </c>
+      <c r="D109" t="n">
+        <v>5695.7</v>
+      </c>
+      <c r="E109" t="n">
+        <v>29.6</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>221.5</v>
+      </c>
+      <c r="C110" t="n">
+        <v>1072.8</v>
+      </c>
+      <c r="D110" t="n">
+        <v>5907.2</v>
+      </c>
+      <c r="E110" t="n">
+        <v>32.2</v>
       </c>
     </row>
   </sheetData>
